--- a/Configs/bullet_event_config.xlsx
+++ b/Configs/bullet_event_config.xlsx
@@ -77,10 +77,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>爆炸 r2</t>
-  </si>
-  <si>
-    <t>爆炸半径2，伤害100%</t>
+    <t>爆炸</t>
+  </si>
+  <si>
+    <t>爆炸半径，伤害100%</t>
   </si>
   <si>
     <t>10000|2</t>
@@ -1362,7 +1362,6 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1"/>
       <c r="D1" t="s">
         <v>2</v>
       </c>
@@ -1380,7 +1379,6 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2"/>
       <c r="D2" t="s">
         <v>6</v>
       </c>

--- a/Configs/bullet_event_config.xlsx
+++ b/Configs/bullet_event_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -80,10 +80,16 @@
     <t>爆炸</t>
   </si>
   <si>
-    <t>爆炸半径，伤害100%</t>
-  </si>
-  <si>
-    <t>10000|2</t>
+    <t>爆炸半径，伤害50%</t>
+  </si>
+  <si>
+    <t>5000|3</t>
+  </si>
+  <si>
+    <t>爆炸半径，伤害10%</t>
+  </si>
+  <si>
+    <t>1000|5</t>
   </si>
   <si>
     <t>追踪</t>
@@ -152,94 +158,28 @@
     <t>10|5</t>
   </si>
   <si>
-    <t>弹射 1</t>
-  </si>
-  <si>
-    <t>弹射1次</t>
-  </si>
-  <si>
-    <t>1|5000|0|9000</t>
-  </si>
-  <si>
-    <t>弹射 2</t>
-  </si>
-  <si>
-    <t>弹射2次</t>
-  </si>
-  <si>
-    <t>2|5000|0|9000</t>
-  </si>
-  <si>
-    <t>弹射 3</t>
-  </si>
-  <si>
-    <t>弹射3次</t>
-  </si>
-  <si>
-    <t>3|5000|0|9000</t>
-  </si>
-  <si>
-    <t>弹射 4</t>
-  </si>
-  <si>
-    <t>弹射4次</t>
-  </si>
-  <si>
-    <t>4|5000|0|9000</t>
-  </si>
-  <si>
     <t>弹射 5</t>
   </si>
   <si>
     <t>弹射5次</t>
   </si>
   <si>
-    <t>5|5000|0|9000</t>
-  </si>
-  <si>
-    <t>弹射 6</t>
-  </si>
-  <si>
-    <t>弹射6次</t>
-  </si>
-  <si>
-    <t>6|5000|0|9000</t>
-  </si>
-  <si>
-    <t>弹射 7</t>
-  </si>
-  <si>
-    <t>弹射7次</t>
-  </si>
-  <si>
-    <t>7|5000|0|9000</t>
-  </si>
-  <si>
-    <t>弹射 8</t>
-  </si>
-  <si>
-    <t>弹射8次</t>
-  </si>
-  <si>
-    <t>8|5000|0|9000</t>
-  </si>
-  <si>
-    <t>弹射 9</t>
-  </si>
-  <si>
-    <t>弹射9次</t>
-  </si>
-  <si>
-    <t>9|5000|0|9000</t>
+    <t>5|3000|0|8000</t>
+  </si>
+  <si>
+    <t>弹射15次</t>
+  </si>
+  <si>
+    <t>15|3000|0|8000</t>
   </si>
   <si>
     <t>弹射 10</t>
   </si>
   <si>
-    <t>弹射10次，伤害不衰减</t>
-  </si>
-  <si>
-    <t>10|10000|0|10000</t>
+    <t>弹射15次，伤害不衰减</t>
+  </si>
+  <si>
+    <t>15|10000|0|10000</t>
   </si>
   <si>
     <t>连射 1</t>
@@ -1349,7 +1289,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="31.625" customWidth="1"/>
@@ -1391,7 +1331,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <f>B3*1000+C3</f>
+        <f t="shared" ref="A3:A7" si="0">B3*1000+C3</f>
         <v>101000</v>
       </c>
       <c r="B3">
@@ -1412,7 +1352,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <f>B4*1000+C4</f>
+        <f t="shared" si="0"/>
         <v>101002</v>
       </c>
       <c r="B4">
@@ -1433,7 +1373,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <f>B5*1000+C5</f>
+        <f t="shared" si="0"/>
         <v>101003</v>
       </c>
       <c r="B5">
@@ -1454,7 +1394,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <f>B6*1000+C6</f>
+        <f t="shared" si="0"/>
         <v>102001</v>
       </c>
       <c r="B6">
@@ -1475,59 +1415,59 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <f>B7*1000+C7</f>
-        <v>103000</v>
+        <f t="shared" si="0"/>
+        <v>102002</v>
       </c>
       <c r="B7">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <f t="shared" ref="A8:A47" si="0">B8*1000+C8</f>
-        <v>201002</v>
+        <f>B8*1000+C8</f>
+        <v>103000</v>
       </c>
       <c r="B8">
-        <v>201</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <f t="shared" si="0"/>
-        <v>201003</v>
+        <f>B9*1000+C9</f>
+        <v>201002</v>
       </c>
       <c r="B9">
         <v>201</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
         <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
@@ -1535,20 +1475,20 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <f t="shared" si="0"/>
-        <v>201004</v>
+        <f>B10*1000+C10</f>
+        <v>201003</v>
       </c>
       <c r="B10">
         <v>201</v>
       </c>
       <c r="C10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -1556,20 +1496,20 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <f t="shared" si="0"/>
-        <v>201005</v>
+        <f>B11*1000+C11</f>
+        <v>201004</v>
       </c>
       <c r="B11">
         <v>201</v>
       </c>
       <c r="C11" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -1577,20 +1517,20 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <f t="shared" si="0"/>
-        <v>201006</v>
+        <f>B12*1000+C12</f>
+        <v>201005</v>
       </c>
       <c r="B12">
         <v>201</v>
       </c>
       <c r="C12" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>32</v>
@@ -1598,20 +1538,20 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <f t="shared" si="0"/>
-        <v>201007</v>
+        <f>B13*1000+C13</f>
+        <v>201006</v>
       </c>
       <c r="B13">
         <v>201</v>
       </c>
       <c r="C13" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -1619,20 +1559,20 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <f t="shared" si="0"/>
-        <v>201008</v>
+        <f t="shared" ref="A14:A19" si="1">B14*1000+C14</f>
+        <v>201007</v>
       </c>
       <c r="B14">
         <v>201</v>
       </c>
       <c r="C14" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
         <v>36</v>
@@ -1640,20 +1580,20 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <f t="shared" si="0"/>
-        <v>201009</v>
+        <f t="shared" si="1"/>
+        <v>201008</v>
       </c>
       <c r="B15">
         <v>201</v>
       </c>
       <c r="C15" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
         <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
         <v>38</v>
@@ -1661,662 +1601,536 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <f t="shared" si="0"/>
-        <v>201010</v>
+        <f t="shared" si="1"/>
+        <v>201009</v>
       </c>
       <c r="B16">
         <v>201</v>
       </c>
       <c r="C16" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>202001</v>
+      <c r="A17">
+        <f t="shared" si="1"/>
+        <v>201010</v>
       </c>
       <c r="B17">
-        <v>202</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
+        <v>201</v>
+      </c>
+      <c r="C17" s="1">
+        <v>10</v>
       </c>
       <c r="D17" t="s">
         <v>41</v>
       </c>
       <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
         <v>42</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>202002</v>
+        <f t="shared" si="1"/>
+        <v>202001</v>
       </c>
       <c r="B18">
         <v>202</v>
       </c>
       <c r="C18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
         <v>44</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>45</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>202003</v>
+        <f t="shared" si="1"/>
+        <v>202002</v>
       </c>
       <c r="B19">
         <v>202</v>
       </c>
       <c r="C19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" t="s">
         <v>47</v>
-      </c>
-      <c r="E19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
-        <v>202004</v>
+        <f t="shared" ref="A20:A41" si="2">B20*1000+C20</f>
+        <v>202003</v>
       </c>
       <c r="B20">
         <v>202</v>
       </c>
       <c r="C20" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" t="s">
         <v>50</v>
-      </c>
-      <c r="E20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
-        <v>202005</v>
-      </c>
-      <c r="B21">
-        <v>202</v>
-      </c>
-      <c r="C21" s="1">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>203001</v>
+      </c>
+      <c r="B21" s="1">
+        <v>203</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
-        <v>202006</v>
-      </c>
-      <c r="B22">
-        <v>202</v>
+        <f t="shared" si="2"/>
+        <v>203002</v>
+      </c>
+      <c r="B22" s="1">
+        <v>203</v>
       </c>
       <c r="C22" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
+        <v>54</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
-        <v>202007</v>
-      </c>
-      <c r="B23">
-        <v>202</v>
+        <f t="shared" si="2"/>
+        <v>203003</v>
+      </c>
+      <c r="B23" s="1">
+        <v>203</v>
       </c>
       <c r="C23" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
+        <v>56</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
-        <v>202008</v>
-      </c>
-      <c r="B24">
-        <v>202</v>
+        <f t="shared" si="2"/>
+        <v>203004</v>
+      </c>
+      <c r="B24" s="1">
+        <v>203</v>
       </c>
       <c r="C24" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
-        <v>202009</v>
-      </c>
-      <c r="B25">
-        <v>202</v>
+        <f t="shared" si="2"/>
+        <v>203005</v>
+      </c>
+      <c r="B25" s="1">
+        <v>203</v>
       </c>
       <c r="C25" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
-        <v>202010</v>
-      </c>
-      <c r="B26">
-        <v>202</v>
+        <f t="shared" si="2"/>
+        <v>203006</v>
+      </c>
+      <c r="B26" s="1">
+        <v>203</v>
       </c>
       <c r="C26" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
-        <v>203001</v>
+        <f t="shared" si="2"/>
+        <v>203007</v>
       </c>
       <c r="B27" s="1">
         <v>203</v>
       </c>
-      <c r="C27">
-        <v>1</v>
+      <c r="C27" s="1">
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
-        <v>203002</v>
+        <f t="shared" si="2"/>
+        <v>203008</v>
       </c>
       <c r="B28" s="1">
         <v>203</v>
       </c>
       <c r="C28" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
-        <v>203003</v>
+        <f t="shared" si="2"/>
+        <v>203009</v>
       </c>
       <c r="B29" s="1">
         <v>203</v>
       </c>
       <c r="C29" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
-        <v>203004</v>
+        <f t="shared" si="2"/>
+        <v>203010</v>
       </c>
       <c r="B30" s="1">
         <v>203</v>
       </c>
       <c r="C30" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
-        <v>203005</v>
-      </c>
-      <c r="B31" s="1">
-        <v>203</v>
+        <f t="shared" si="2"/>
+        <v>204002</v>
+      </c>
+      <c r="B31">
+        <v>204</v>
       </c>
       <c r="C31" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
+        <v>72</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
-        <v>203006</v>
-      </c>
-      <c r="B32" s="1">
-        <v>203</v>
+        <f t="shared" si="2"/>
+        <v>204003</v>
+      </c>
+      <c r="B32">
+        <v>204</v>
       </c>
       <c r="C32" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32">
-        <v>6</v>
+        <v>74</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
-        <v>203007</v>
-      </c>
-      <c r="B33" s="1">
-        <v>203</v>
+        <f t="shared" si="2"/>
+        <v>204004</v>
+      </c>
+      <c r="B33">
+        <v>204</v>
       </c>
       <c r="C33" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33">
-        <v>7</v>
+        <v>76</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
-        <v>203008</v>
-      </c>
-      <c r="B34" s="1">
-        <v>203</v>
+        <f t="shared" si="2"/>
+        <v>204005</v>
+      </c>
+      <c r="B34">
+        <v>204</v>
       </c>
       <c r="C34" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34">
-        <v>8</v>
+        <v>79</v>
+      </c>
+      <c r="F34" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
-        <f t="shared" si="0"/>
-        <v>203009</v>
-      </c>
-      <c r="B35" s="1">
-        <v>203</v>
+        <f t="shared" si="2"/>
+        <v>204006</v>
+      </c>
+      <c r="B35">
+        <v>204</v>
       </c>
       <c r="C35" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35">
-        <v>9</v>
+        <v>82</v>
+      </c>
+      <c r="F35" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
-        <f t="shared" si="0"/>
-        <v>203010</v>
-      </c>
-      <c r="B36" s="1">
-        <v>203</v>
+        <f t="shared" si="2"/>
+        <v>204007</v>
+      </c>
+      <c r="B36">
+        <v>204</v>
       </c>
       <c r="C36" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E36" t="s">
-        <v>90</v>
-      </c>
-      <c r="F36">
-        <v>10</v>
+        <v>85</v>
+      </c>
+      <c r="F36" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
-        <f t="shared" si="0"/>
-        <v>204002</v>
+        <f t="shared" si="2"/>
+        <v>204008</v>
       </c>
       <c r="B37">
         <v>204</v>
       </c>
       <c r="C37" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E37" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
-        <f t="shared" si="0"/>
-        <v>204003</v>
+        <f t="shared" si="2"/>
+        <v>204009</v>
       </c>
       <c r="B38">
         <v>204</v>
       </c>
       <c r="C38" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1">
-        <f t="shared" si="0"/>
-        <v>204004</v>
+        <f t="shared" si="2"/>
+        <v>204010</v>
       </c>
       <c r="B39">
         <v>204</v>
       </c>
       <c r="C39" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D39" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" t="s">
         <v>95</v>
-      </c>
-      <c r="E39" t="s">
-        <v>96</v>
-      </c>
-      <c r="F39" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1">
-        <f t="shared" si="0"/>
-        <v>204005</v>
+        <f t="shared" si="2"/>
+        <v>301000</v>
       </c>
       <c r="B40">
-        <v>204</v>
-      </c>
-      <c r="C40" s="1">
-        <v>5</v>
+        <v>301</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E40" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1">
-        <f t="shared" si="0"/>
-        <v>204006</v>
+        <f t="shared" si="2"/>
+        <v>302000</v>
       </c>
       <c r="B41">
-        <v>204</v>
-      </c>
-      <c r="C41" s="1">
-        <v>6</v>
+        <v>302</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
-      </c>
-      <c r="F41" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1">
-        <f t="shared" si="0"/>
-        <v>204007</v>
-      </c>
-      <c r="B42">
-        <v>204</v>
-      </c>
-      <c r="C42" s="1">
-        <v>7</v>
-      </c>
-      <c r="D42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E42" t="s">
-        <v>105</v>
-      </c>
-      <c r="F42" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1">
-        <f t="shared" si="0"/>
-        <v>204008</v>
-      </c>
-      <c r="B43">
-        <v>204</v>
-      </c>
-      <c r="C43" s="1">
-        <v>8</v>
-      </c>
-      <c r="D43" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" t="s">
-        <v>108</v>
-      </c>
-      <c r="F43" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1">
-        <f t="shared" si="0"/>
-        <v>204009</v>
-      </c>
-      <c r="B44">
-        <v>204</v>
-      </c>
-      <c r="C44" s="1">
-        <v>9</v>
-      </c>
-      <c r="D44" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" t="s">
-        <v>111</v>
-      </c>
-      <c r="F44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1">
-        <f t="shared" si="0"/>
-        <v>204010</v>
-      </c>
-      <c r="B45">
-        <v>204</v>
-      </c>
-      <c r="C45" s="1">
-        <v>10</v>
-      </c>
-      <c r="D45" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" t="s">
-        <v>114</v>
-      </c>
-      <c r="F45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1">
-        <f t="shared" si="0"/>
-        <v>301000</v>
-      </c>
-      <c r="B46">
-        <v>301</v>
-      </c>
-      <c r="D46" t="s">
-        <v>116</v>
-      </c>
-      <c r="E46" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1">
-        <f t="shared" si="0"/>
-        <v>302000</v>
-      </c>
-      <c r="B47">
-        <v>302</v>
-      </c>
-      <c r="D47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E47" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
